--- a/downloads/CyberReperes_Catalogue_Normes.xlsx
+++ b/downloads/CyberReperes_Catalogue_Normes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="ISO-IEC 27000" sheetId="1" state="visible" r:id="rId2"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="949">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -836,6 +836,9 @@
     <t xml:space="preserve">2010</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.iso.org/fr/standard/51582.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pertinente pour l'analyse d'architectures.</t>
   </si>
   <si>
@@ -1841,7 +1844,7 @@
     <t xml:space="preserve">62443-2-1; 3-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Statut à vérifier lors de l'achat.</t>
+    <t xml:space="preserve">RAS</t>
   </si>
   <si>
     <t xml:space="preserve">IEC-62443-2-3</t>
@@ -2892,7 +2895,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2922,12 +2925,6 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2978,7 +2975,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2997,14 +2994,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3152,12 +3141,12 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="63.3"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="6" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="8" min="8" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="1" width="30"/>
@@ -4251,24 +4240,24 @@
         <v>55</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>18</v>
@@ -4277,13 +4266,13 @@
         <v>246</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>163</v>
@@ -4292,24 +4281,24 @@
         <v>55</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>18</v>
@@ -4318,39 +4307,39 @@
         <v>246</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>18</v>
@@ -4359,39 +4348,39 @@
         <v>246</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>18</v>
@@ -4400,13 +4389,13 @@
         <v>246</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>239</v>
@@ -4415,80 +4404,80 @@
         <v>55</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>118</v>
@@ -4497,244 +4486,244 @@
         <v>55</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>239</v>
@@ -4743,39 +4732,39 @@
         <v>55</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>239</v>
@@ -4784,39 +4773,39 @@
         <v>55</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>151</v>
@@ -4825,39 +4814,39 @@
         <v>55</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>85</v>
@@ -4866,39 +4855,39 @@
         <v>55</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>217</v>
@@ -4907,39 +4896,39 @@
         <v>55</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>44</v>
@@ -4948,39 +4937,39 @@
         <v>55</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>239</v>
@@ -4989,24 +4978,24 @@
         <v>55</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>18</v>
@@ -5015,54 +5004,54 @@
         <v>171</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>256</v>
@@ -5071,39 +5060,39 @@
         <v>24</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>163</v>
@@ -5112,39 +5101,39 @@
         <v>24</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>118</v>
@@ -5153,39 +5142,39 @@
         <v>55</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>85</v>
@@ -5194,39 +5183,39 @@
         <v>55</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>118</v>
@@ -5235,39 +5224,39 @@
         <v>24</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>118</v>
@@ -5276,39 +5265,39 @@
         <v>24</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>118</v>
@@ -5317,121 +5306,121 @@
         <v>24</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>55</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>151</v>
@@ -5440,39 +5429,39 @@
         <v>55</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>217</v>
@@ -5481,39 +5470,39 @@
         <v>55</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>217</v>
@@ -5522,36 +5511,36 @@
         <v>55</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>239</v>
@@ -5560,36 +5549,36 @@
         <v>55</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>44</v>
@@ -5601,10 +5590,10 @@
         <v>25</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -5626,7 +5615,7 @@
     <hyperlink ref="M22" r:id="rId14" display="https://www.iso.org/fr/standard/76070.html"/>
     <hyperlink ref="M23" r:id="rId15" display="https://www.iso.org/fr/standard/63461.html"/>
     <hyperlink ref="M24" r:id="rId16" display="https://www.iso.org/fr/standard/51581.html"/>
-    <hyperlink ref="M25" r:id="rId17" display="https://www.iso.org/fr/standard/51581.html"/>
+    <hyperlink ref="M25" r:id="rId17" display="https://www.iso.org/fr/standard/51582.html"/>
     <hyperlink ref="M26" r:id="rId18" display="https://www.iso.org/fr/standard/51583.html"/>
     <hyperlink ref="M27" r:id="rId19" display="https://www.iso.org/fr/standard/51584.html"/>
     <hyperlink ref="M28" r:id="rId20" display="https://www.iso.org/fr/standard/51585.html"/>
@@ -5687,13 +5676,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5701,10 +5690,10 @@
         <v>30</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5712,87 +5701,87 @@
         <v>69</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -5889,43 +5878,43 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>228</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>224</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>37</v>
@@ -5933,31 +5922,31 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>224</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>226</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>151</v>
@@ -5969,83 +5958,83 @@
         <v>228</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>224</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>224</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>161</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>54</v>
@@ -6057,10 +6046,10 @@
         <v>228</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -6165,90 +6154,90 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>149</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>149</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -6352,31 +6341,31 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>256</v>
@@ -6385,42 +6374,42 @@
         <v>24</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>264</v>
@@ -6429,42 +6418,42 @@
         <v>24</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>186</v>
@@ -6473,42 +6462,42 @@
         <v>24</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>118</v>
@@ -6517,42 +6506,42 @@
         <v>24</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>118</v>
@@ -6561,42 +6550,42 @@
         <v>24</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>151</v>
@@ -6605,145 +6594,145 @@
         <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -6852,31 +6841,31 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>264</v>
@@ -6885,42 +6874,42 @@
         <v>24</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>264</v>
@@ -6929,42 +6918,42 @@
         <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>264</v>
@@ -6973,42 +6962,42 @@
         <v>24</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>264</v>
@@ -7017,42 +7006,42 @@
         <v>24</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>264</v>
@@ -7061,42 +7050,42 @@
         <v>24</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>264</v>
@@ -7105,42 +7094,42 @@
         <v>24</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>264</v>
@@ -7149,218 +7138,218 @@
         <v>24</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>151</v>
@@ -7369,13 +7358,13 @@
         <v>55</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7482,31 +7471,31 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>226</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>4</v>
@@ -7515,42 +7504,42 @@
         <v>55</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>4</v>
@@ -7559,42 +7548,42 @@
         <v>55</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>195</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>4</v>
@@ -7603,541 +7592,541 @@
         <v>55</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N4" s="4" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>781</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>786</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>787</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>762</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>789</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>790</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>792</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>793</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>796</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>798</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>799</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>801</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>802</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>793</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>805</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>806</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>807</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>810</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>813</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>814</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>816</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>818</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>820</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>821</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>822</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>793</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>824</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>825</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>826</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>807</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>827</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>829</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>830</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>831</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>832</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>834</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>837</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>838</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>841</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>842</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>843</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>846</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>849</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>851</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>852</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>853</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>854</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>814</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>855</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>856</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>858</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>859</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>860</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>861</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>814</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>862</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>863</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>865</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>866</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>867</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>868</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>869</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>870</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>871</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>872</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>875</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>876</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>877</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>878</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>880</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>881</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>882</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>883</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>885</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>886</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>887</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>779</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>888</v>
+      <c r="N16" s="3" t="s">
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -8252,31 +8241,31 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>85</v>
@@ -8285,13 +8274,13 @@
         <v>24</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -8331,7 +8320,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="26.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="26.24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8394,75 +8383,75 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>161</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>217</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>161</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>239</v>
@@ -8471,13 +8460,13 @@
         <v>24</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
   </sheetData>
@@ -8511,40 +8500,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
   </sheetData>
